--- a/filesystem/MarketingOps/CRM/client_renewal_dates.xlsx
+++ b/filesystem/MarketingOps/CRM/client_renewal_dates.xlsx
@@ -156,7 +156,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="28">
     <border>
       <left/>
       <right/>
@@ -264,11 +264,141 @@
         <color rgb="000EA5E9"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00CBD5E1"/>
+      </left>
+      <right style="thin">
+        <color rgb="00CBD5E1"/>
+      </right>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00CBD5E1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00CBD5E1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00CBD5E1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00CBD5E1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00CBD5E1"/>
+      </left>
+      <right style="thin">
+        <color rgb="00CBD5E1"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00CBD5E1"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00CBD5E1"/>
+      </left>
+      <right style="thin">
+        <color rgb="00CBD5E1"/>
+      </right>
+      <bottom style="thin">
+        <color rgb="00CBD5E1"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="000EA5E9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00CBD5E1"/>
+      </left>
+      <right style="thin">
+        <color rgb="00CBD5E1"/>
+      </right>
+      <bottom/>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="00CBD5E1"/>
+      </right>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00CBD5E1"/>
+      </left>
+      <right style="thin">
+        <color rgb="00CBD5E1"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="00CBD5E1"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <right/>
+      <bottom style="medium">
+        <color rgb="000EA5E9"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -384,6 +514,51 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -711,13 +886,6 @@
           <t>Thornfield Life Sciences Marketing — Client Renewal Date Record (CRM Extract)</t>
         </is>
       </c>
-      <c r="B1" s="11" t="n"/>
-      <c r="C1" s="11" t="n"/>
-      <c r="D1" s="11" t="n"/>
-      <c r="E1" s="11" t="n"/>
-      <c r="F1" s="11" t="n"/>
-      <c r="G1" s="11" t="n"/>
-      <c r="H1" s="11" t="n"/>
     </row>
     <row r="2" ht="12" customHeight="1"/>
     <row r="3" ht="22" customHeight="1">
@@ -726,17 +894,17 @@
           <t>Source system:</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="B3" s="57" t="inlineStr">
         <is>
           <t>ERPNext (erp.thornfieldlsm.com) — Customer master + Sales Order (custom field: renewal_date)</t>
         </is>
       </c>
-      <c r="C3" s="14" t="n"/>
-      <c r="D3" s="14" t="n"/>
-      <c r="E3" s="14" t="n"/>
-      <c r="F3" s="14" t="n"/>
-      <c r="G3" s="14" t="n"/>
-      <c r="H3" s="15" t="n"/>
+      <c r="C3" s="45" t="n"/>
+      <c r="D3" s="45" t="n"/>
+      <c r="E3" s="45" t="n"/>
+      <c r="F3" s="45" t="n"/>
+      <c r="G3" s="45" t="n"/>
+      <c r="H3" s="46" t="n"/>
     </row>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="16" t="inlineStr">
@@ -744,17 +912,12 @@
           <t>Prepared by:</t>
         </is>
       </c>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="58" t="inlineStr">
         <is>
           <t>Grace Feldman, Director, Analytics &amp; Reporting</t>
         </is>
       </c>
-      <c r="C4" s="18" t="n"/>
-      <c r="D4" s="18" t="n"/>
-      <c r="E4" s="18" t="n"/>
-      <c r="F4" s="18" t="n"/>
-      <c r="G4" s="18" t="n"/>
-      <c r="H4" s="19" t="n"/>
+      <c r="H4" s="48" t="n"/>
     </row>
     <row r="5" ht="42" customHeight="1">
       <c r="A5" s="16" t="inlineStr">
@@ -762,17 +925,12 @@
           <t>Scope:</t>
         </is>
       </c>
-      <c r="B5" s="20" t="inlineStr">
+      <c r="B5" s="59" t="inlineStr">
         <is>
           <t>Active client accounts with a Sales Order carrying a populated renewal_date field. Includes migrated Bramwell customer records (account_origin = "Inherited — Bramwell") and Thornfield-native records.</t>
         </is>
       </c>
-      <c r="C5" s="18" t="n"/>
-      <c r="D5" s="18" t="n"/>
-      <c r="E5" s="18" t="n"/>
-      <c r="F5" s="18" t="n"/>
-      <c r="G5" s="18" t="n"/>
-      <c r="H5" s="19" t="n"/>
+      <c r="H5" s="48" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="21" t="inlineStr">
@@ -780,17 +938,17 @@
           <t>Rows:</t>
         </is>
       </c>
-      <c r="B6" s="22" t="inlineStr">
+      <c r="B6" s="50" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="C6" s="23" t="n"/>
-      <c r="D6" s="23" t="n"/>
-      <c r="E6" s="23" t="n"/>
-      <c r="F6" s="23" t="n"/>
-      <c r="G6" s="23" t="n"/>
-      <c r="H6" s="24" t="n"/>
+      <c r="C6" s="51" t="n"/>
+      <c r="D6" s="51" t="n"/>
+      <c r="E6" s="51" t="n"/>
+      <c r="F6" s="51" t="n"/>
+      <c r="G6" s="51" t="n"/>
+      <c r="H6" s="52" t="n"/>
     </row>
     <row r="7" ht="16" customHeight="1"/>
     <row r="8" ht="28" customHeight="1">
@@ -867,7 +1025,7 @@
       </c>
       <c r="H9" s="32" t="inlineStr">
         <is>
-          <t>Rachel Okafor</t>
+          <t>Meredith Halloran</t>
         </is>
       </c>
     </row>
@@ -903,7 +1061,7 @@
       </c>
       <c r="H10" s="38" t="inlineStr">
         <is>
-          <t>Priya Ramaswamy</t>
+          <t>James Fitzpatrick</t>
         </is>
       </c>
     </row>
@@ -939,7 +1097,7 @@
       </c>
       <c r="H11" s="32" t="inlineStr">
         <is>
-          <t>Rachel Okafor</t>
+          <t>Meredith Halloran</t>
         </is>
       </c>
     </row>
@@ -975,7 +1133,7 @@
       </c>
       <c r="H12" s="38" t="inlineStr">
         <is>
-          <t>James Delacroix</t>
+          <t>Priscilla Choi</t>
         </is>
       </c>
     </row>
@@ -1011,7 +1169,7 @@
       </c>
       <c r="H13" s="32" t="inlineStr">
         <is>
-          <t>Meera Sundaram</t>
+          <t>Terrance Bloom</t>
         </is>
       </c>
     </row>
@@ -1023,7 +1181,7 @@
       </c>
       <c r="B14" s="34" t="inlineStr">
         <is>
-          <t>Redcliff BioProducts</t>
+          <t>Cordwell Lab Systems</t>
         </is>
       </c>
       <c r="C14" s="35" t="inlineStr">
@@ -1047,7 +1205,7 @@
       </c>
       <c r="H14" s="38" t="inlineStr">
         <is>
-          <t>Rachel Okafor</t>
+          <t>Nadia Petrov</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1241,7 @@
       </c>
       <c r="H15" s="32" t="inlineStr">
         <is>
-          <t>James Delacroix</t>
+          <t>Colin Ashworth</t>
         </is>
       </c>
     </row>
@@ -1119,7 +1277,7 @@
       </c>
       <c r="H16" s="38" t="inlineStr">
         <is>
-          <t>Meera Sundaram</t>
+          <t>Deirdre O'Sullivan</t>
         </is>
       </c>
     </row>
@@ -1155,7 +1313,7 @@
       </c>
       <c r="H17" s="32" t="inlineStr">
         <is>
-          <t>Priya Ramaswamy</t>
+          <t>James Fitzpatrick</t>
         </is>
       </c>
     </row>
@@ -1191,7 +1349,7 @@
       </c>
       <c r="H18" s="38" t="inlineStr">
         <is>
-          <t>James Delacroix</t>
+          <t>Kevin Rasmussen</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1385,7 @@
       </c>
       <c r="H19" s="32" t="inlineStr">
         <is>
-          <t>Rachel Okafor</t>
+          <t>Meredith Halloran</t>
         </is>
       </c>
     </row>
@@ -1263,7 +1421,7 @@
       </c>
       <c r="H20" s="38" t="inlineStr">
         <is>
-          <t>Priya Ramaswamy</t>
+          <t>James Fitzpatrick</t>
         </is>
       </c>
     </row>
@@ -1275,7 +1433,7 @@
       </c>
       <c r="B21" s="28" t="inlineStr">
         <is>
-          <t>Whitecrest Diagnostics</t>
+          <t>Hollowfield Therapeutics</t>
         </is>
       </c>
       <c r="C21" s="29" t="inlineStr">
@@ -1299,14 +1457,14 @@
       </c>
       <c r="H21" s="32" t="inlineStr">
         <is>
-          <t>Meera Sundaram</t>
+          <t>Priscilla Choi</t>
         </is>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1">
       <c r="A22" s="33" t="inlineStr">
         <is>
-          <t>CUST-2025-0129</t>
+          <t>CUST-2025-0298</t>
         </is>
       </c>
       <c r="B22" s="34" t="inlineStr">
@@ -1515,7 +1673,7 @@
       </c>
       <c r="H27" s="32" t="inlineStr">
         <is>
-          <t>Sofia Bergen</t>
+          <t>Anika Whitworth</t>
         </is>
       </c>
     </row>
@@ -1558,7 +1716,7 @@
     <row r="29" ht="22" customHeight="1">
       <c r="A29" s="27" t="inlineStr">
         <is>
-          <t>CUST-2025-0179</t>
+          <t>CUST-2025-0299</t>
         </is>
       </c>
       <c r="B29" s="28" t="inlineStr">
@@ -1731,7 +1889,7 @@
       </c>
       <c r="H33" s="32" t="inlineStr">
         <is>
-          <t>Meera Sundaram</t>
+          <t>Priscilla Choi</t>
         </is>
       </c>
     </row>
@@ -1803,7 +1961,7 @@
       </c>
       <c r="H35" s="32" t="inlineStr">
         <is>
-          <t>Rachel Okafor</t>
+          <t>Terrance Bloom</t>
         </is>
       </c>
     </row>
@@ -1839,7 +1997,7 @@
       </c>
       <c r="H36" s="38" t="inlineStr">
         <is>
-          <t>James Delacroix</t>
+          <t>Nadia Petrov</t>
         </is>
       </c>
     </row>
@@ -1851,7 +2009,7 @@
       </c>
       <c r="B37" s="28" t="inlineStr">
         <is>
-          <t>Blackwater Bio</t>
+          <t>Alderway BioResearch</t>
         </is>
       </c>
       <c r="C37" s="29" t="inlineStr">
@@ -1892,7 +2050,7 @@
       </c>
       <c r="C38" s="35" t="inlineStr">
         <is>
-          <t>Thornfield native</t>
+          <t>Inherited — Bramwell</t>
         </is>
       </c>
       <c r="D38" s="36" t="n">
@@ -1911,108 +2069,84 @@
       </c>
       <c r="H38" s="38" t="inlineStr">
         <is>
-          <t>Meera Sundaram</t>
+          <t>Sofia Bergen</t>
         </is>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1"/>
     <row r="40" ht="26" customHeight="1">
-      <c r="A40" s="39" t="inlineStr">
+      <c r="A40" s="60" t="inlineStr">
         <is>
           <t>Field notes</t>
         </is>
       </c>
-      <c r="B40" s="39" t="n"/>
-      <c r="C40" s="39" t="n"/>
-      <c r="D40" s="39" t="n"/>
-      <c r="E40" s="39" t="n"/>
-      <c r="F40" s="39" t="n"/>
-      <c r="G40" s="39" t="n"/>
-      <c r="H40" s="39" t="n"/>
+      <c r="B40" s="53" t="n"/>
+      <c r="C40" s="53" t="n"/>
+      <c r="D40" s="53" t="n"/>
+      <c r="E40" s="53" t="n"/>
+      <c r="F40" s="53" t="n"/>
+      <c r="G40" s="53" t="n"/>
+      <c r="H40" s="53" t="n"/>
     </row>
     <row r="41" ht="38" customHeight="1">
-      <c r="A41" s="40" t="inlineStr">
+      <c r="A41" s="61" t="inlineStr">
         <is>
           <t>Account Origin: sourced from the ERPNext Customer doctype custom field account_origin (values: "Thornfield native" / "Inherited — Bramwell"). Records with the "Inherited — Bramwell" designation were migrated from the pre-close Bramwell Scientific Marketing ERPNext instance on 08/25/2025 and carry Thornfield-format Customer IDs post-migration.</t>
         </is>
       </c>
-      <c r="B41" s="14" t="n"/>
-      <c r="C41" s="14" t="n"/>
-      <c r="D41" s="14" t="n"/>
-      <c r="E41" s="14" t="n"/>
-      <c r="F41" s="14" t="n"/>
-      <c r="G41" s="14" t="n"/>
-      <c r="H41" s="15" t="n"/>
+      <c r="B41" s="45" t="n"/>
+      <c r="C41" s="45" t="n"/>
+      <c r="D41" s="45" t="n"/>
+      <c r="E41" s="45" t="n"/>
+      <c r="F41" s="45" t="n"/>
+      <c r="G41" s="45" t="n"/>
+      <c r="H41" s="46" t="n"/>
     </row>
     <row r="42" ht="22" customHeight="1">
-      <c r="A42" s="41" t="inlineStr">
+      <c r="A42" s="62" t="inlineStr">
         <is>
           <t>Current Term Start: the effective start date of the term underlying the current active Sales Order.</t>
         </is>
       </c>
-      <c r="B42" s="18" t="n"/>
-      <c r="C42" s="18" t="n"/>
-      <c r="D42" s="18" t="n"/>
-      <c r="E42" s="18" t="n"/>
-      <c r="F42" s="18" t="n"/>
-      <c r="G42" s="18" t="n"/>
-      <c r="H42" s="19" t="n"/>
+      <c r="H42" s="48" t="n"/>
     </row>
     <row r="43" ht="42" customHeight="1">
-      <c r="A43" s="41" t="inlineStr">
+      <c r="A43" s="62" t="inlineStr">
         <is>
           <t>Renewal Date: the value of the Sales Order custom field renewal_date — the effective date of the renewal event for the term. For records where the renewal event has already occurred, the field reflects the locked-in effective date recorded against that Sales Order.</t>
         </is>
       </c>
-      <c r="B43" s="18" t="n"/>
-      <c r="C43" s="18" t="n"/>
-      <c r="D43" s="18" t="n"/>
-      <c r="E43" s="18" t="n"/>
-      <c r="F43" s="18" t="n"/>
-      <c r="G43" s="18" t="n"/>
-      <c r="H43" s="19" t="n"/>
+      <c r="H43" s="48" t="n"/>
     </row>
     <row r="44" ht="22" customHeight="1">
-      <c r="A44" s="41" t="inlineStr">
+      <c r="A44" s="62" t="inlineStr">
         <is>
           <t>Renewal Term (months): term length as recorded on the current Sales Order.</t>
         </is>
       </c>
-      <c r="B44" s="18" t="n"/>
-      <c r="C44" s="18" t="n"/>
-      <c r="D44" s="18" t="n"/>
-      <c r="E44" s="18" t="n"/>
-      <c r="F44" s="18" t="n"/>
-      <c r="G44" s="18" t="n"/>
-      <c r="H44" s="19" t="n"/>
+      <c r="H44" s="48" t="n"/>
     </row>
     <row r="45" ht="52" customHeight="1">
-      <c r="A45" s="41" t="inlineStr">
+      <c r="A45" s="62" t="inlineStr">
         <is>
           <t>ERPNext Sales Order ID: the underlying Sales Order carrying the renewal_date value. Sales Orders in the SO-2024-xxxx series were created in the Thornfield instance prior to migration; SO-2025-xxxx numbering covers both Thornfield-originated Sales Orders issued in 2025 and Bramwell-originated Sales Orders re-keyed at migration cutover.</t>
         </is>
       </c>
-      <c r="B45" s="18" t="n"/>
-      <c r="C45" s="18" t="n"/>
-      <c r="D45" s="18" t="n"/>
-      <c r="E45" s="18" t="n"/>
-      <c r="F45" s="18" t="n"/>
-      <c r="G45" s="18" t="n"/>
-      <c r="H45" s="19" t="n"/>
+      <c r="H45" s="48" t="n"/>
     </row>
     <row r="46" ht="22" customHeight="1">
-      <c r="A46" s="42" t="inlineStr">
+      <c r="A46" s="56" t="inlineStr">
         <is>
           <t>Owner: the ERPNext Customer-record owner (account manager of record).</t>
         </is>
       </c>
-      <c r="B46" s="23" t="n"/>
-      <c r="C46" s="23" t="n"/>
-      <c r="D46" s="23" t="n"/>
-      <c r="E46" s="23" t="n"/>
-      <c r="F46" s="23" t="n"/>
-      <c r="G46" s="23" t="n"/>
-      <c r="H46" s="24" t="n"/>
+      <c r="B46" s="51" t="n"/>
+      <c r="C46" s="51" t="n"/>
+      <c r="D46" s="51" t="n"/>
+      <c r="E46" s="51" t="n"/>
+      <c r="F46" s="51" t="n"/>
+      <c r="G46" s="51" t="n"/>
+      <c r="H46" s="52" t="n"/>
     </row>
     <row r="47" ht="16" customHeight="1"/>
     <row r="48" ht="22" customHeight="1">
@@ -2021,13 +2155,6 @@
           <t>Extract generated from ERPNext report crm_renewal_dates on 01/09/2026 by Grace Feldman.</t>
         </is>
       </c>
-      <c r="B48" s="43" t="n"/>
-      <c r="C48" s="43" t="n"/>
-      <c r="D48" s="43" t="n"/>
-      <c r="E48" s="43" t="n"/>
-      <c r="F48" s="43" t="n"/>
-      <c r="G48" s="43" t="n"/>
-      <c r="H48" s="43" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A8:H38"/>

--- a/filesystem/MarketingOps/CRM/client_renewal_dates.xlsx
+++ b/filesystem/MarketingOps/CRM/client_renewal_dates.xlsx
@@ -1658,10 +1658,10 @@
         </is>
       </c>
       <c r="D27" s="30" t="n">
-        <v>45545</v>
+        <v>45337</v>
       </c>
       <c r="E27" s="30" t="n">
-        <v>46275</v>
+        <v>46067</v>
       </c>
       <c r="F27" s="31" t="n">
         <v>24</v>

--- a/filesystem/MarketingOps/CRM/client_renewal_dates.xlsx
+++ b/filesystem/MarketingOps/CRM/client_renewal_dates.xlsx
@@ -1601,7 +1601,7 @@
       </c>
       <c r="H25" s="32" t="inlineStr">
         <is>
-          <t>Sofia Bergen</t>
+          <t>Cyrus Delacroix</t>
         </is>
       </c>
     </row>
@@ -2069,7 +2069,7 @@
       </c>
       <c r="H38" s="38" t="inlineStr">
         <is>
-          <t>Sofia Bergen</t>
+          <t>Reid Alderman</t>
         </is>
       </c>
     </row>

--- a/filesystem/MarketingOps/CRM/client_renewal_dates.xlsx
+++ b/filesystem/MarketingOps/CRM/client_renewal_dates.xlsx
@@ -1757,7 +1757,7 @@
       </c>
       <c r="B30" s="34" t="inlineStr">
         <is>
-          <t>Meridian Biolabs</t>
+          <t>Ashgrove Biolabs</t>
         </is>
       </c>
       <c r="C30" s="35" t="inlineStr">

--- a/filesystem/MarketingOps/CRM/client_renewal_dates.xlsx
+++ b/filesystem/MarketingOps/CRM/client_renewal_dates.xlsx
@@ -22,7 +22,7 @@
     <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
     <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="18">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -118,6 +118,12 @@
       <color rgb="0064748B"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Segoe UI"/>
+      <i val="1"/>
+      <color rgb="FF475569"/>
+      <sz val="9"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -398,7 +404,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -559,6 +565,9 @@
     </xf>
     <xf numFmtId="0" fontId="15" fillId="4" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2150,7 +2159,7 @@
     </row>
     <row r="47" ht="16" customHeight="1"/>
     <row r="48" ht="22" customHeight="1">
-      <c r="A48" s="43" t="inlineStr">
+      <c r="A48" s="63" t="inlineStr">
         <is>
           <t>Extract generated from ERPNext report crm_renewal_dates on 01/09/2026 by Grace Feldman.</t>
         </is>
